--- a/src/attributions/attributions_ig_traj_403.xlsx
+++ b/src/attributions/attributions_ig_traj_403.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG15"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,25 +2137,25 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06817736829919668</v>
+        <v>0.2215036480915525</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0131523175880039</v>
+        <v>-0.000326215600983291</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06566044146921518</v>
+        <v>-0.2422962408211856</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
@@ -2164,28 +2164,28 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0296171086930416</v>
+        <v>0.2870785671806664</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.015903194786389</v>
+        <v>-0.03932231689557485</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06913185017249233</v>
+        <v>-0.2214589384879978</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>-0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006384963433124175</v>
+        <v>-0.01640885314007656</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,37 +2203,37 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-9.698408631474894e-12</v>
+        <v>-1.418422969816111e-10</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.001316413439561255</v>
+        <v>0.0172773308856136</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02388387343436447</v>
+        <v>-0.06243651190273351</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02792959074103706</v>
+        <v>-0.1188583556000809</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.00247903818412815</v>
+        <v>-0.08303628294888724</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.00354777264718351</v>
+        <v>0.009546101107901384</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.02084677388912812</v>
+        <v>-0.06727612874504955</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01152220348885222</v>
+        <v>-0.06856040258062261</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,88 +2275,88 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.06452269179905887</v>
+        <v>0.4413757196145507</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01446258652331276</v>
+        <v>-0.09327721541493211</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.04994025735755922</v>
+        <v>-0.1555262648159682</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0160611284633702</v>
+        <v>0.009935368955582247</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02135282427511212</v>
+        <v>-0.03862652042668014</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.01787064023150686</v>
+        <v>-0.05823361089036776</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04351860165752339</v>
+        <v>0.1087593062567917</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00932338962355388</v>
+        <v>0.1194542608992216</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0124965605743812</v>
+        <v>0.1670512178486828</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.03871092640192611</v>
+        <v>0.1763110639383546</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,16 +2365,16 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.02087941462605746</v>
+        <v>-0.1543745208087224</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.009469855595248537</v>
+        <v>-0.3117860539499107</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01506402021245821</v>
+        <v>-0.09606207152039214</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
@@ -2392,10 +2392,10 @@
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.00259072301709946</v>
+        <v>-0.03170149457924635</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03739158189059448</v>
+        <v>0.1771971197072123</v>
       </c>
       <c r="CJ4" t="n">
         <v>0</v>
@@ -2404,202 +2404,202 @@
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.007116151944535803</v>
+        <v>-0.2504445935906303</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.01261031521107712</v>
+        <v>0.08936485478898638</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.005167638879234704</v>
+        <v>0.141541101710174</v>
       </c>
       <c r="CS4" t="n">
         <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.008492926170353908</v>
+        <v>-0.09717591758728805</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.006880018646247143</v>
+        <v>-0.03769152132387502</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03499845367271342</v>
+        <v>0.1630792624861292</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.0144040562301518</v>
+        <v>0.005122317424082291</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0055898862586951</v>
+        <v>-0.1282655077925839</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.06743485126625685</v>
+        <v>0.06971863268863439</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01117671022084722</v>
+        <v>-0.05162040326205575</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01752651401258854</v>
+        <v>0.0890308909485205</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0129567236186389</v>
+        <v>0.2027211703953482</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.008587715165533718</v>
+        <v>-0.001877350484190133</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.009617141761593383</v>
+        <v>0.000392411548636445</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.0347698630537207</v>
+        <v>-0.1027112818652782</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0001106170419303974</v>
+        <v>-0.1124589987585309</v>
       </c>
       <c r="EH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.004634337231542574</v>
+        <v>-0.1033494013953214</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.006572290515366866</v>
+        <v>0.1212812803571133</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001178453677252778</v>
+        <v>0.02312642366693501</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01438031504423733</v>
+        <v>-0.1095896002794506</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.03800366117251338</v>
+        <v>0.1303739356510969</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.009222572167477891</v>
+        <v>-0.1097119321227708</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.003378081020453382</v>
+        <v>-0.06903522609712448</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0319557649577359</v>
+        <v>0.1551572939089634</v>
       </c>
       <c r="FD4" t="n">
         <v>0</v>
@@ -2620,25 +2620,25 @@
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01182207257189984</v>
+        <v>-0.1409632494418332</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.02070916785665378</v>
+        <v>-0.02095215570204309</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.006795276865964437</v>
+        <v>-0.01698495684030469</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,52 +2647,52 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001520469135012262</v>
+        <v>0.0748086706811722</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.00307829838192898</v>
+        <v>0.06901047286122794</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.04743015248462611</v>
+        <v>0.1614679494243401</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.02417151070826672</v>
+        <v>0.01853438450897311</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.006043427185503298</v>
+        <v>0.133445507869355</v>
       </c>
       <c r="GE4" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,16 +2709,16 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1873311670650538</v>
+        <v>0.1047907517282135</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06358625590703348</v>
+        <v>-0.05052857970633175</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08801939443441424</v>
+        <v>-0.02866285429869367</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,16 +2736,16 @@
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09767308955450306</v>
+        <v>0.09261216438184008</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04875423382252699</v>
+        <v>-0.05303989496947035</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1015628860244703</v>
+        <v>-0.04729190930411054</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,28 +2760,28 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.009449014767357549</v>
+        <v>0.009118935159432734</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.072157667061936e-11</v>
+        <v>1.301346496599078e-12</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0004724884008374676</v>
+        <v>0.001611466061439422</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,43 +2790,43 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.05090605954800644</v>
+        <v>-0.01598820924560519</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0775413025718521</v>
+        <v>-0.05214847301086382</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1307687981902418</v>
+        <v>-0.05984091526094552</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.02048087464065855</v>
+        <v>0.061047157750758</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03032813097293459</v>
+        <v>-0.008557941105769488</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.05998174257369632</v>
+        <v>0.04367755137319317</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
@@ -2835,31 +2835,31 @@
         <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.2583863943366981</v>
+        <v>0.1191609817239891</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09237926387005529</v>
+        <v>0.001861336161003752</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1831599984607465</v>
+        <v>-0.07238015884957461</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003274893548011172</v>
+        <v>-0.01828740392922825</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1522490818401873</v>
+        <v>-0.0614550593933053</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.07604337584236701</v>
+        <v>-0.01505735743950618</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2898,22 +2898,22 @@
         <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1212762761300591</v>
+        <v>0.01371311226774823</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01328239063378319</v>
+        <v>0.04191579300800236</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1783873933487395</v>
+        <v>0.06972267833969278</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,19 +2925,19 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.169696194188285</v>
+        <v>0.1441166246645424</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.008597472981506003</v>
+        <v>0.012278684446079</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01101554269228368</v>
+        <v>0.005945663135644309</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2946,25 +2946,25 @@
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05824875829882258</v>
+        <v>-0.05795762929917055</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.0005165479527153031</v>
+        <v>0.04294513550680955</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01169206555370133</v>
+        <v>0.02594271180325167</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
@@ -2979,43 +2979,43 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04151916137340914</v>
+        <v>-0.08232377704871968</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1066485269973158</v>
+        <v>0.0790363915752947</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1919478600922161</v>
+        <v>0.05453317014060515</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03184856109265805</v>
+        <v>-0.05578951341392144</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.008166047347019893</v>
+        <v>0.05064589068341382</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.03636055513043886</v>
+        <v>0.03149170944196879</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3024,25 +3024,25 @@
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001482439081979541</v>
+        <v>-0.0008630923021569698</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0371749011984535</v>
+        <v>-0.002774066771235354</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01331763393427136</v>
+        <v>-0.03817823513069444</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
@@ -3057,25 +3057,25 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.08605492471808812</v>
+        <v>-0.06659359022353373</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.04160669794235169</v>
+        <v>0.04319348943221336</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.04895917775762935</v>
+        <v>-0.0050613560918945</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
@@ -3087,52 +3087,52 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02889679547931091</v>
+        <v>0.03343619594488099</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.01824938401172765</v>
+        <v>0.03606940230843054</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.06573583487499969</v>
+        <v>-0.04302232197160417</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.02894635670975156</v>
+        <v>-0.005653481496791586</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.02889630642556935</v>
+        <v>0.02717671796565907</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07680309220671336</v>
+        <v>0.05419279713917827</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,43 +3141,43 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02746512971830712</v>
+        <v>-0.0485850083661833</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.02341079801183845</v>
+        <v>0.02228641999960212</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.03601345953116687</v>
+        <v>-0.000747489959124751</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.03600188218839418</v>
+        <v>-0.06592076292940555</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01436955342623091</v>
+        <v>0.05970761469899664</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.03684445056486234</v>
+        <v>0.01972335783436713</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
@@ -3186,111 +3186,111 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.009370815306885043</v>
+        <v>-0.007040310236005641</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.04672465571763405</v>
+        <v>-0.002403968702306384</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.02548862343299103</v>
+        <v>-0.01692513478569325</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.06400904574100864</v>
+        <v>0.01484157986511285</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.04066728803189115</v>
+        <v>0.06199110152000763</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.08732716087109864</v>
+        <v>-0.09014402523129902</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY5" t="n">
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.01247801500298819</v>
+        <v>-0.01754961102431505</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.06274833313740349</v>
+        <v>0.00594136013263284</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01630664063190194</v>
+        <v>0.04125610962645442</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01887158642398301</v>
+        <v>0.02815715471976052</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009689625114348522</v>
+        <v>-0.01725230920628036</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003557559734007315</v>
+        <v>0.06267333758835898</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02603065821413193</v>
+        <v>0.01576816509784219</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01392504960704725</v>
+        <v>-0.01702248186803054</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0009717344678422765</v>
+        <v>0.0006477898131069791</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0003521384412388784</v>
+        <v>-0.005344382817776814</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.00174993069250878</v>
+        <v>-0.000491960192778865</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>-0</v>
@@ -3359,25 +3359,25 @@
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02818927293602419</v>
+        <v>-0.01487477680645257</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.03508865291161517</v>
+        <v>-0.06675880921590428</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.004127084608617568</v>
+        <v>-0.01731638969900468</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0003512314270371948</v>
+        <v>0.009688452068511801</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,37 +3395,37 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01807734016048768</v>
+        <v>-0.008705249042193088</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.003414026356682362</v>
+        <v>-0.01647790937743114</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.03658345012257944</v>
+        <v>0.07990392647553334</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.009228480603634426</v>
+        <v>-0.01502284174495536</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.005253524591758744</v>
+        <v>-0.01341083457023028</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3434,28 +3434,28 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0008907578754677882</v>
+        <v>-0.005558512124281887</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.0196858625264174</v>
+        <v>-0.01371359299285525</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.001877034710632937</v>
+        <v>-0.002308909740949133</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,52 +3464,52 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04075065313171525</v>
+        <v>0.01991209789495917</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01468315814132989</v>
+        <v>0.04230519916075115</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01288049573654493</v>
+        <v>0.03411236591738441</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01056708448949826</v>
+        <v>0.04664232458562121</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01780745825149483</v>
+        <v>0.003205655453932625</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01866263036378899</v>
+        <v>-0.03157185468991649</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.002045909303514875</v>
+        <v>-0.01210494486252812</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>5.198403694807939e-05</v>
+        <v>-0.004154049855283141</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006359510457585205</v>
+        <v>0.02462953476385568</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>-0</v>
@@ -3545,52 +3545,52 @@
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.002423024560358169</v>
+        <v>-0.04011403950562271</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00544689122714799</v>
+        <v>0.05766412448058476</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01333241421287421</v>
+        <v>0.0235678365963265</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.00841160380000837</v>
+        <v>-0.015427016233757</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0009620152489947096</v>
+        <v>-0.006605558640728702</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.003804321859797987</v>
+        <v>0.02154951587595079</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.003291440540760907</v>
+        <v>-0.02089022527755464</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0002873827004281968</v>
+        <v>-0.00153662221841639</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0305551854467712</v>
+        <v>0.001540502279116942</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,28 +3623,28 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.004713209731326677</v>
+        <v>-0.01594655020693623</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.02320432817469132</v>
+        <v>-0.001150724293142444</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.00743669253951203</v>
+        <v>0.02950458439331507</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,28 +3653,28 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01250994962086509</v>
+        <v>-0.013439416495961</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.008077238941951444</v>
+        <v>0.01244858480626178</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.00655966052003658</v>
+        <v>0.02757932405065934</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,34 +3683,34 @@
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.009249743303363298</v>
+        <v>-0.01027779884286028</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0009756393243415597</v>
+        <v>-0.02429011674505055</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.003447156709041451</v>
+        <v>0.003331918861701998</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.001548352391965243</v>
+        <v>-0.00130985161273192</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
@@ -3719,40 +3719,40 @@
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.02015362651874953</v>
+        <v>-0.0001909898796356951</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03295679903374411</v>
+        <v>0.008370133245846484</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.008479914511066751</v>
+        <v>-0.01927807939264871</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0004954404088539452</v>
+        <v>-0.01191140163843316</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.008627500203531445</v>
+        <v>0.01655020723177312</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.003892984825206752</v>
+        <v>-0.02174676885470158</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01910855657457327</v>
+        <v>0.01963183727335722</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01824844302985401</v>
+        <v>-0.002828940197416678</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01294433299612246</v>
+        <v>0.009855222337573284</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0007286634990725826</v>
+        <v>0.0003735620981089868</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.009494881552001882</v>
+        <v>-0.05004920761263874</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02505959382195102</v>
+        <v>0.01056103483701351</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.003327441001117107</v>
+        <v>0.01155939988600426</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1598441782534993</v>
+        <v>0.07547085300286868</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01295469866843689</v>
+        <v>-0.03404612967965201</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03229302089970802</v>
+        <v>-0.009928768660842116</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06491573162366926</v>
+        <v>0.1095266552599719</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.08579572347660949</v>
+        <v>-0.03519395085868061</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0414464576488667</v>
+        <v>-0.006855788635576726</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01690207329232787</v>
+        <v>-0.006200340502091749</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.007112190065739504</v>
+        <v>-0.01343209567396345</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0004404195113827708</v>
+        <v>0.000113830724794694</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07260533574054107</v>
+        <v>-0.02370423914014669</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.03089643276420275</v>
+        <v>-0.02171194139846258</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.02091155930235896</v>
+        <v>-0.001835082945937783</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03527237911418751</v>
+        <v>0.02198656284816985</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02123115175749627</v>
+        <v>-0.007934627216246002</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01545843621013622</v>
+        <v>-0.008803807072488826</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2055580941533943</v>
+        <v>0.1070413537652433</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09426503569172268</v>
+        <v>-0.008443219908430357</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,22 +4003,22 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.004239302032551793</v>
+        <v>0.01421388142809313</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0329580318815053</v>
+        <v>-0.009522137536404584</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.06893531175282486</v>
+        <v>-0.02633847314682952</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,70 +4027,70 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-3.779176076098112e-11</v>
+        <v>-1.965091928273036e-11</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02200036820780597</v>
+        <v>0.01587213658930427</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1279808205786425</v>
+        <v>0.05106598763362692</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.01782181634533119</v>
+        <v>0.0168580774828061</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1500567312669785</v>
+        <v>0.06694476243393988</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.008906048018662916</v>
+        <v>-0.02974659612995779</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01404206612626842</v>
+        <v>-0.02127513526805559</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03795618709292421</v>
+        <v>-0.02994744625948313</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002275319812897261</v>
+        <v>0.01118677314095089</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.03862912060577354</v>
+        <v>0.01725481850553115</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02938741275551267</v>
+        <v>-0.0579314666458526</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.03331718869211479</v>
+        <v>0.008878144655570486</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01482317834823331</v>
+        <v>0.02700645237045292</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03413781981068066</v>
+        <v>-0.03123230594595079</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.00938902464382267</v>
+        <v>0.005615942958582159</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4165,121 +4165,121 @@
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.03401074970527295</v>
+        <v>0.01620565874583469</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1304320533788376</v>
+        <v>-0.02470722960233976</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.06281691749830565</v>
+        <v>-0.01483270322373618</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.01712383314904424</v>
+        <v>-0.006451914710730536</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.006106995153658585</v>
+        <v>-0.01516824919053698</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.008646745232967171</v>
+        <v>0.0101039062305353</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.02035937653954237</v>
+        <v>-0.02887050089395588</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.001293759560160577</v>
+        <v>0.0151573400747706</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01228749681083532</v>
+        <v>0.006151187907267661</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.008992368870732766</v>
+        <v>-0.01216929411531222</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.00151481227746463</v>
+        <v>-0.03120652877784115</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03683582946231873</v>
+        <v>0.00578703582167569</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.04467219529405728</v>
+        <v>0.01021576542336716</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.06350337611852183</v>
+        <v>-0.005138869349833338</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.001227567690204946</v>
+        <v>0.01103841154276279</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.02489336968491425</v>
+        <v>0.001109833481290338</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0474362860636997</v>
+        <v>-0.03539363098012444</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,10 +4315,10 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.004286771195223887</v>
+        <v>0.001155306297139365</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01979332688753379</v>
+        <v>0.01637662714000711</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04667870808198245</v>
+        <v>-0.02435096434409474</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01894734010178563</v>
+        <v>0.003033966211903987</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.04867358785099894</v>
+        <v>0.05116943498618706</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.07430292456645607</v>
+        <v>0.01874800160477474</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,10 +4369,10 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0265023303915967</v>
+        <v>-0.01372769912384108</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.002206943367201865</v>
+        <v>0.001418731688528497</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.06906699239757963</v>
+        <v>-0.01470151050607581</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03324018377132183</v>
+        <v>-0.002529738153782128</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5779386492176219</v>
+        <v>0.1852492820617278</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.269515840155497</v>
+        <v>-0.1114077640607451</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.009261807338841748</v>
+        <v>-0.04599639360801929</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3460078482666382</v>
+        <v>0.1881164425913034</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2498525784849327</v>
+        <v>-0.1535202568949517</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1137715829367261</v>
+        <v>-0.08610003642760819</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06721673331852601</v>
+        <v>0.03424509708884484</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.02012696018387201</v>
+        <v>-0.00676508870535465</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.04363310307380162</v>
+        <v>-0.02062620081304014</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,43 +5066,43 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1965463539748594</v>
+        <v>-0.02827008491883094</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02418989208752166</v>
+        <v>-0.06092407268905083</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01451801942690739</v>
+        <v>-0.09947573294803863</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.03993523155895554</v>
+        <v>0.09659610903591552</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.06948443311200087</v>
+        <v>-0.06184460087585517</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1000359528496079</v>
+        <v>0.03744848388312925</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,19 +5120,19 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.5114235279313086</v>
+        <v>0.1642132689865035</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01187893776293625</v>
+        <v>-0.04360365791318766</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2235912401898792</v>
+        <v>-0.1622227147633208</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5144,19 +5144,19 @@
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01627370865739572</v>
+        <v>-0.03483483574220898</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.1055908518248953</v>
+        <v>-0.008375715601377372</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.2223767395597387</v>
+        <v>-0.004821768221915804</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1893077565111072</v>
+        <v>0.04643819865537138</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.05749193676311605</v>
+        <v>0.01981027644349505</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1866260949878613</v>
+        <v>0.04318583698212621</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.3503705078487032</v>
+        <v>0.2070487016312644</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.04429193212990635</v>
+        <v>-0.1491009701099817</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.04657628436098563</v>
+        <v>-0.05416370790099619</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,22 +5228,22 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1364138288666397</v>
+        <v>-0.06789151487362738</v>
       </c>
       <c r="CF9" t="n">
         <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03548303915818336</v>
+        <v>0.0954575033861618</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.03256514414796104</v>
+        <v>0.02564580122309569</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,49 +5255,49 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.04865984857754554</v>
+        <v>-0.08396967877950569</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1885056184311422</v>
+        <v>0.2267976116074884</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1202235793885938</v>
+        <v>0.08903335217511497</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1043972137295159</v>
+        <v>-0.05106242340391616</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.06637937816721108</v>
+        <v>0.1043315846406933</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.01551756544570414</v>
+        <v>0.03934153402631177</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5306,25 +5306,25 @@
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02521634712751207</v>
+        <v>-0.006334631441139971</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.07572956202845867</v>
+        <v>0.009129048828840431</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05138532784029763</v>
+        <v>-0.03539706792000852</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.1014559959623916</v>
+        <v>-0.08021614125211908</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.005456613520234227</v>
+        <v>0.05738873927965761</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.04908706905658708</v>
+        <v>0.04448219108311589</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5360,28 +5360,28 @@
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.003397612924782084</v>
+        <v>0.00546918144146193</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.02695069078864664</v>
+        <v>0.02783742652137342</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.01236281404844134</v>
+        <v>-0.03879281646536498</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,49 +5390,49 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03612922582675968</v>
+        <v>0.0169792808796183</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03814159494438138</v>
+        <v>0.07414004419783198</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05868695677237222</v>
+        <v>0.03561495401723355</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.1456851279089308</v>
+        <v>-0.06817503176187502</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.1040062940784021</v>
+        <v>-0.08770058312843924</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.03402579424686605</v>
+        <v>0.001360579755956128</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,46 +5444,46 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1150603336273399</v>
+        <v>-0.067520614245679</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0574666065290985</v>
+        <v>0.1160412922632763</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.005785701627105936</v>
+        <v>0.01970841681157766</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.01178924977796799</v>
+        <v>-0.0285372441285415</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.05825967718056939</v>
+        <v>0.03282416872941744</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.02709492680039003</v>
+        <v>-0.05593142901730057</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
         <v>-0</v>
@@ -5492,28 +5492,28 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
         <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.0692897960346671</v>
+        <v>0.02643939526958115</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.05475188955413969</v>
+        <v>0.1048112243767195</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1525205062709087</v>
+        <v>-0.09531376207830428</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
         <v>0</v>
@@ -5522,31 +5522,31 @@
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.05155715963055582</v>
+        <v>-0.004096546104775137</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07284108468546746</v>
+        <v>0.03516718844388114</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8824914124715041</v>
+        <v>0.2136487863777217</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.107604902159495</v>
+        <v>-0.1744388435280359</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2503950352976547</v>
+        <v>-0.0331606091979801</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,25 +5572,25 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.002230972004913776</v>
+        <v>0.01779457091775865</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4691075057992343</v>
+        <v>0.1853413479437359</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2065033536721434</v>
+        <v>-0.2817998735427354</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3381481321109409</v>
+        <v>-0.07387540874955932</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,115 +5599,115 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.004053207363134539</v>
+        <v>-0.0001326073810071791</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1585185552769114</v>
+        <v>0.068871716767785</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04662201226652574</v>
+        <v>-0.03354954330591105</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.002288980259213516</v>
+        <v>-0.09393478660065087</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.002668415307919241</v>
+        <v>0.001594847830240478</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2079182216309994</v>
+        <v>-0.1282175358363264</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.04998814491798044</v>
+        <v>-0.0384622745311101</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.0765746542613351</v>
+        <v>-0.140373435492239</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01232558491078395</v>
+        <v>0.02854165279989443</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.04079430947175432</v>
+        <v>0.07453287767911186</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.07499949389257658</v>
+        <v>-0.03194149733948082</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1470749459857488</v>
+        <v>0.02110496440124425</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.03304423625339807</v>
+        <v>0.00676789931203017</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.7855866555936711</v>
+        <v>0.1659588915619907</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1850755905095575</v>
+        <v>-0.07992267316022203</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1636572495861528</v>
+        <v>-0.178897602340502</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1397076638081912</v>
+        <v>-0.02832501372145118</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.15217354016164</v>
+        <v>-0.03000253979425646</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1876904220444807</v>
+        <v>-0.09081043939589137</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.4110000937007634</v>
+        <v>-0.02485464728145516</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01355374237404313</v>
+        <v>-0.007368255741271536</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5961495049172667</v>
+        <v>0.05712768883145775</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1931267606105497</v>
+        <v>0.06960060677209778</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.3548566108617254</v>
+        <v>0.0221969009158394</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.07122168472805795</v>
+        <v>0.03640837880186291</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,97 +5770,97 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5083589316265239</v>
+        <v>0.2046911562339166</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0305635750944434</v>
+        <v>-0.03391385831487854</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.01022804719236843</v>
+        <v>-0.1344214432220047</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.06855147339808323</v>
+        <v>-0.07985247266529454</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.2107099724865732</v>
+        <v>-0.06164658277376661</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.04417831381049478</v>
+        <v>0.1201050920351007</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.004395804553019675</v>
+        <v>0.03240813148306282</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01993089594845424</v>
+        <v>-0.02308670547995965</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.248989378859096</v>
+        <v>-0.00744418652145352</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.2103570033077206</v>
+        <v>0.1894827668216151</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05736818023973751</v>
+        <v>0.2264570349647145</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.09159061953024743</v>
+        <v>0.02614402044836544</v>
       </c>
       <c r="CU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.1245024802321199</v>
+        <v>-0.05543445754549824</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02616088548925471</v>
+        <v>0.1325614612319759</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.009751616793497349</v>
+        <v>0.04076261797798447</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,106 +5869,106 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.03531605375510617</v>
+        <v>-0.01621860174430065</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.2262662389564301</v>
+        <v>-0.04277767244440275</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.02742814771988729</v>
+        <v>0.04485312945231813</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.02294845841214642</v>
+        <v>-0.007220349991547271</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.01746713198300616</v>
+        <v>-0.04108333601806086</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.2198814427943946</v>
+        <v>-0.03749085234917902</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03112291219436134</v>
+        <v>0.05361810877931078</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01195321368497838</v>
+        <v>-0.05545278756741649</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.09459294016344508</v>
+        <v>0.09642593448975773</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.03958807526753103</v>
+        <v>0.04634100320883981</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.06265120066359631</v>
+        <v>0.05249799054010133</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.2097132400345102</v>
+        <v>-0.07790688398615135</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.04192594901251027</v>
+        <v>0.112597313484213</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1067432654739419</v>
+        <v>0.03091469278857844</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0.02737938540497484</v>
+        <v>0.09765227880509157</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.07089478814237535</v>
+        <v>0.01606265472184706</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,142 +5977,142 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.06310825824763396</v>
+        <v>-0.03499201330376227</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1523538945487365</v>
+        <v>-0.04809639729413526</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.06025598255904904</v>
+        <v>0.1105137877254755</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.02888615806846641</v>
+        <v>-0.03499154347146529</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.02649402600951551</v>
+        <v>0.009758127814100143</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.1410873690879125</v>
+        <v>-0.0690719415304495</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.008036629692781161</v>
+        <v>0.1572390551970858</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.07838557517818326</v>
+        <v>0.03009350289860253</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.008835347435687889</v>
+        <v>-0.01396910821385794</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.1054994500512249</v>
+        <v>-0.03286570770956074</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.1161821291749501</v>
+        <v>-0.08123345098129836</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.07604595251374997</v>
+        <v>0.07038230890598503</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.05666775912527096</v>
+        <v>-0.03591865967895871</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.2763850111367944</v>
+        <v>0.06568744319312739</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.2564386912681113</v>
+        <v>0.1383775309382013</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.2430110994256044</v>
+        <v>-0.1555492646537666</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.04009350333472448</v>
+        <v>-0.06076527832801941</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1381322721563844</v>
+        <v>-0.03125632750087293</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.1518669249826131</v>
+        <v>0.05021338788965155</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.08237590980716299</v>
+        <v>-0.05224337048746057</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2361746729042613</v>
+        <v>0.6148578298666948</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1562668303376581</v>
+        <v>0.1100286797560684</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1054179094778749</v>
+        <v>-0.4988155615191294</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,19 +6150,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.147615926254542</v>
+        <v>0.7108480489036988</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.162300666609006</v>
+        <v>-0.05285377761187396</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1113416187313764</v>
+        <v>-0.4550086404076653</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04429862826823606</v>
+        <v>0.1199610238802292</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006395362578906352</v>
+        <v>-0.122973923703254</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0374729425164069</v>
+        <v>0.0003358723769625742</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.05426991948375505</v>
+        <v>-0.06637404678784145</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03264936664952681</v>
+        <v>-0.4018245578618944</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0290165343968256</v>
+        <v>0.1023685186440555</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6228,10 +6228,10 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03361344622091719</v>
+        <v>0.1130922679082844</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,13 +6240,13 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02840051706029986</v>
+        <v>-0.04040988067838387</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.01659144481375837</v>
+        <v>-0.05383151044449424</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2010050706582955</v>
+        <v>0.5664514533554763</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -6267,25 +6267,25 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01589592748538095</v>
+        <v>-0.2811874123596437</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.008424009239999735</v>
+        <v>-0.07173781340402768</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05872271904879162</v>
+        <v>-0.007052811056391752</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1255201547763204</v>
+        <v>-0.008621854081419657</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.08343898685464807</v>
+        <v>-0.1895428635865113</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1381687058225971</v>
+        <v>0.201523285051151</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.09524963311976517</v>
+        <v>0.2233243807033938</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.04455769733595424</v>
+        <v>0.1624359287666348</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1268713679640782</v>
+        <v>0.510793175309489</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,16 +6348,16 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01626362973512931</v>
+        <v>-0.05584800660526817</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02584788790421731</v>
+        <v>-0.1575559515158339</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
@@ -6366,49 +6366,49 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.04310568812007162</v>
+        <v>-0.200537274306232</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01857463382003858</v>
+        <v>-0.04809415751391415</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02837642790597469</v>
+        <v>0.1781456461359549</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.057895550688405</v>
+        <v>-0.3155803844162669</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.06425753392821913</v>
+        <v>0.1093691045307186</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.01729511344050071</v>
+        <v>0.04142515173129303</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02282319409729685</v>
+        <v>-0.1744942860651168</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01759833932814578</v>
+        <v>-0.05813047392022324</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0311353033511972</v>
+        <v>0.1834717329474197</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,46 +6447,46 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.06177946914354954</v>
+        <v>-0.1835147477381881</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01828349314499414</v>
+        <v>-0.2498112653450764</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.004039184034173708</v>
+        <v>0.01333263348436706</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05671702525455457</v>
+        <v>-0.1376236441571603</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02172193921499949</v>
+        <v>-0.04190988162970787</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.05131459537071589</v>
+        <v>-0.0479144761736925</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,82 +6498,82 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.01286734803099763</v>
+        <v>0.06213673060565445</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.05051365756545777</v>
+        <v>0.06318066493833639</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.04037387148924711</v>
+        <v>0.1228227181197897</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.006115964904214565</v>
+        <v>-0.009281671661683449</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01327764770986725</v>
+        <v>-0.1437103940620246</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.007929798652410495</v>
+        <v>0.1285359040500001</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.02087309233603008</v>
+        <v>-0.04950586133384909</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.0001501512886039088</v>
+        <v>-0.2331300706404818</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0495291464281629</v>
+        <v>0.09158682688921854</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
@@ -6582,52 +6582,52 @@
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01792852028599255</v>
+        <v>-0.2248754219964125</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01581282378742448</v>
+        <v>-0.1047283158174376</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0387907961408977</v>
+        <v>0.1427109726770109</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03946722410080174</v>
+        <v>-0.2075475800240949</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04817475118491016</v>
+        <v>0.2134221785039373</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03118899602278949</v>
+        <v>0.1207708880664495</v>
       </c>
       <c r="FM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,34 +6636,34 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.001874430614839957</v>
+        <v>0.112011892984587</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.007757056706915528</v>
+        <v>-0.05031884719382472</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01653993114899934</v>
+        <v>0.02140733967202406</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.07139944682268501</v>
+        <v>-0.1157873520551121</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,13 +6675,13 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.03187526981252528</v>
+        <v>0.1833193992888438</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG11" t="n">
         <v>0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4857038494992004</v>
+        <v>0.2234517937198061</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2563330195388681</v>
+        <v>-0.09129276243838455</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1299919261128079</v>
+        <v>-0.06393878330458722</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6719,16 +6719,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3233719684606484</v>
+        <v>0.2299148785100664</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2371382925045132</v>
+        <v>-0.1382134728484891</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1750348690711721</v>
+        <v>-0.0886373656380329</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,73 +6743,73 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1235949212683369</v>
+        <v>0.05573503203265207</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0003794002677546875</v>
+        <v>-0.01291005888843665</v>
       </c>
       <c r="W12" t="n">
-        <v>0.01294929450906681</v>
+        <v>-0.02355655701392858</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1761068328867836</v>
+        <v>-0.01115030333574363</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.02551370186668115</v>
+        <v>-0.1110237300678982</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.02038438388779524</v>
+        <v>-0.09309739807143971</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.03611453048599594</v>
+        <v>0.09518556130997906</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.04347796015630944</v>
+        <v>-0.0521951234770628</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.07494884477442108</v>
+        <v>0.05458686860289587</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,25 +6818,25 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3955957338876275</v>
+        <v>0.1690009699061386</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01818812565845158</v>
+        <v>-0.01638185674762289</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0948909675839103</v>
+        <v>-0.07885905523033632</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02046942612455082</v>
+        <v>-0.03190690992233242</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1168920717990579</v>
+        <v>-0.0512941526614919</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2553209419938666</v>
+        <v>-0.0539205273413461</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,52 +6881,52 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1633734636919955</v>
+        <v>0.03921265983681555</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.06218775608208536</v>
+        <v>-0.005286788049364651</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1107531925975605</v>
+        <v>0.1102766250990652</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2594043417525262</v>
+        <v>0.2091969702025677</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.005002336169420282</v>
+        <v>-0.02296084083861542</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.05177299767287475</v>
+        <v>-0.01484523132977887</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1087146245230123</v>
+        <v>-0.08216921437754374</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01400830105711887</v>
+        <v>0.06797806719927742</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01519916184780809</v>
+        <v>0.03482758908728555</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,25 +6956,25 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.06717732809015693</v>
+        <v>-0.140401760411384</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.2060798406736226</v>
+        <v>0.1938631185455704</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.09625531800910977</v>
+        <v>0.05428195520729187</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,46 +6989,46 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.06653435898954452</v>
+        <v>-0.06064895790360849</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.0439411222918135</v>
+        <v>0.0716768498161931</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01397086488451107</v>
+        <v>0.03902315260453226</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.07041385051135868</v>
+        <v>-0.009878160464480172</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03703715419613036</v>
+        <v>-0.006578738709980592</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04049477219723273</v>
+        <v>-0.0461407453907268</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
@@ -7043,103 +7043,103 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.08469818193017416</v>
+        <v>-0.08280357287101928</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.05403601554365203</v>
+        <v>0.05777059256135775</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.05469351931380013</v>
+        <v>0.02055579021148898</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01564753520826137</v>
+        <v>0.04709381342633848</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.07909026901754741</v>
+        <v>-0.02629976854635252</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.00264733298489378</v>
+        <v>-0.03250230024172544</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03951647963308749</v>
+        <v>-0.003956234854859124</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.06046634883875845</v>
+        <v>0.05832613659028219</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.08720314064106567</v>
+        <v>0.0806657495331955</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07604612716557349</v>
+        <v>-0.05001568140711455</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.05072740552368688</v>
+        <v>0.04162866640966141</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.04178438928247994</v>
+        <v>-0.001925209300494668</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,70 +7151,70 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.07716661902219166</v>
+        <v>-0.08570697583606032</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04077450092008683</v>
+        <v>0.08495479669474854</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.005493078634962364</v>
+        <v>0.02354836477342506</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02309808811103473</v>
+        <v>-0.02071401042302798</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06434650272317458</v>
+        <v>0.007899175537918145</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.04291381873278065</v>
+        <v>-0.04581921946012944</v>
       </c>
       <c r="FL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05995889039095603</v>
+        <v>-0.00152322906689469</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.07121830700809655</v>
+        <v>0.04216941449687606</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.07065239482110064</v>
+        <v>-0.1178369478168401</v>
       </c>
       <c r="FU12" t="n">
         <v>-0</v>
@@ -7229,19 +7229,19 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.0002854322034155686</v>
+        <v>-0.06062688456340099</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.04501170384570371</v>
+        <v>0.01633840384108702</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
         <v>-0</v>
@@ -7250,10 +7250,10 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6491960033571327</v>
+        <v>0.6755971884253114</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1312304420365067</v>
+        <v>0.2107104126554888</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5594843168731225</v>
+        <v>-0.745042335780926</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,22 +7285,22 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4849395752201171</v>
+        <v>0.8634471118572621</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.07988375542136238</v>
+        <v>-0.02605548147916361</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5391786834736506</v>
+        <v>-0.7061655266681068</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -7312,28 +7312,28 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06593330586667155</v>
+        <v>0.2687855410910474</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.09363407223687761</v>
+        <v>-0.3686792353431892</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01723469502272012</v>
+        <v>-0.05669135850601424</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,22 +7342,22 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.08122989464182849</v>
+        <v>0.02389709807049893</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03741514197557504</v>
+        <v>-0.7970532794723384</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02752077832993841</v>
+        <v>-0.3428172433397541</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.07169165727170312</v>
+        <v>0.2284843916064218</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.02050562571342299</v>
+        <v>0.08863220993472672</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.0629431842194268</v>
+        <v>-0.1686975952917313</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7396,7 +7396,7 @@
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.3783372195420173</v>
+        <v>1.054186359790588</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,43 +7405,43 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.04756890543563139</v>
+        <v>-0.1831789285701884</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1864357053543872</v>
+        <v>-0.1741167466289435</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1670451617721851</v>
+        <v>-0.3541806551953244</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1479790856720332</v>
+        <v>-0.4351671056072507</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.164787100273906</v>
+        <v>-0.4584955573387434</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,34 +7450,34 @@
         <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1598483365010419</v>
+        <v>0.09218788384544965</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0640329688911507</v>
+        <v>0.08403007421080608</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.001668064508788722</v>
+        <v>0.101494330497905</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2590205497236936</v>
+        <v>0.7292437088420677</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,64 +7486,64 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.0896416996995486</v>
+        <v>-0.1477824712511654</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.230966366929363</v>
+        <v>-0.4919513425738059</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1129566115789963</v>
+        <v>-0.2524080327065756</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01417396591112596</v>
+        <v>0.0189468255395239</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1248595666281788</v>
+        <v>0.2721813226880569</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.05138453155906408</v>
+        <v>-0.6053457335043624</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02534296191756753</v>
+        <v>0.8858057190129631</v>
       </c>
       <c r="CR13" t="n">
-        <v>6.366517331145366e-05</v>
+        <v>0.5088554629078951</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,82 +7555,82 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.08754162367198952</v>
+        <v>-0.2302407590413069</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005186253581491549</v>
+        <v>-0.02330111502294916</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1309222278306025</v>
+        <v>0.2486150613098535</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.0517039075820707</v>
+        <v>-0.02434297972967084</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05209906785760798</v>
+        <v>-0.2596655585442429</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.01426197159839024</v>
+        <v>0.05510179037420288</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02774394468693214</v>
+        <v>-0.1030241777669141</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01835016116360393</v>
+        <v>-0.09431658742222475</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.03110256012082827</v>
+        <v>0.278541618336428</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,25 +7639,25 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01300385275426536</v>
+        <v>0.1105262491903032</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0288656880586945</v>
+        <v>-0.06779647867018584</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03680524524745121</v>
+        <v>0.2091066695012278</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,19 +7666,19 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0706198682164359</v>
+        <v>-0.05151024493549833</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03453375079535356</v>
+        <v>-0.151008173037228</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1264628598824051</v>
+        <v>0.0346036145738335</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7693,22 +7693,22 @@
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.04253599476362236</v>
+        <v>-0.008073634689593309</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.03893436034583932</v>
+        <v>-0.0855756728035526</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04139980972365207</v>
+        <v>0.2021158916740595</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,52 +7720,52 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.08174576648939942</v>
+        <v>-0.2731124939134204</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0004839230238072151</v>
+        <v>-0.0313971628771583</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1118845114361426</v>
+        <v>0.2492126092989334</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.07933232617218546</v>
+        <v>-0.3724439474216834</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.007607603232923316</v>
+        <v>0.1508308774438221</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.1108738765643392</v>
+        <v>0.0663988098896621</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01767128780985657</v>
+        <v>0.1227137998918399</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,10 +7783,10 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01549042984246401</v>
+        <v>0.2408742452282544</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01872596307773345</v>
+        <v>-0.06620191426491369</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.007100860807210156</v>
+        <v>-0.1116905882759836</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01977042331759551</v>
+        <v>0.09573304122189238</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,162 +7822,162 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.056244141391589</v>
+        <v>0.7920007126615495</v>
       </c>
       <c r="C14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6339838382422479</v>
+        <v>-0.5312939014939547</v>
       </c>
       <c r="E14" t="n">
-        <v>0.293416937254075</v>
+        <v>-0.2579160770262934</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6314235289095365</v>
+        <v>0.6876624734488798</v>
       </c>
       <c r="L14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5447950976001968</v>
+        <v>-0.6840651593431574</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2587881215301581</v>
+        <v>-0.3270369544315089</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1829585142669923</v>
+        <v>0.1191051918171068</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1623940812155586</v>
+        <v>-0.1466261689939619</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1720196442715254</v>
+        <v>-0.09209951100188646</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.03962368754734631</v>
+        <v>-0.06910400308726426</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.1210128390164647</v>
+        <v>-0.08720242702151083</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.06019232678469218</v>
+        <v>-0.05587347086291297</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.110471084084112</v>
+        <v>0.2633716638586612</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.06869619276235232</v>
+        <v>-0.1021987539248737</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.06420343274659523</v>
+        <v>0.1615258962248308</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.6985688582229974</v>
+        <v>0.6298808186887938</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.08727032550914847</v>
+        <v>-0.1402364587300687</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.07230496233130501</v>
+        <v>-0.1630262794661989</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7989,22 +7989,22 @@
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>-0.1279318912866895</v>
+        <v>-0.06018360853865504</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.3153233738213863</v>
+        <v>-0.1565669797301428</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.3931877233091462</v>
+        <v>-0.2701424748696887</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI14" t="n">
         <v>-0</v>
@@ -8019,22 +8019,22 @@
         <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0.1366184817325605</v>
+        <v>-0.105689339314266</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04134178617385426</v>
+        <v>0.07636442928625387</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1066098162024428</v>
+        <v>0.07955919766890185</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,82 +8043,82 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0.5186050444803466</v>
+        <v>0.5308096255387237</v>
       </c>
       <c r="BW14" t="n">
         <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.06068250867844311</v>
+        <v>-0.2577477879821568</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.04326517389709278</v>
+        <v>-0.06325054121750531</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.2006118465306387</v>
+        <v>-0.3042069366397429</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.1300078409472474</v>
+        <v>0.1768945169167211</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.02411916163839141</v>
+        <v>0.04440747836221348</v>
       </c>
       <c r="CI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.07957014402321512</v>
+        <v>-0.3270761993747502</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.005423345855697382</v>
+        <v>0.3295216457107552</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.04532506662251511</v>
+        <v>0.1945434234890455</v>
       </c>
       <c r="CR14" t="n">
         <v>-0</v>
       </c>
       <c r="CS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
@@ -8127,25 +8127,25 @@
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.1717675426007182</v>
+        <v>-0.2979182435389835</v>
       </c>
       <c r="CX14" t="n">
         <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.1542748801600555</v>
+        <v>0.1838537600966113</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.01340364935668867</v>
+        <v>0.06172087459837232</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,70 +8154,70 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.02057139658114979</v>
+        <v>0.01029059300901858</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.1138316212522552</v>
+        <v>0.03495040709266174</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.07874040845482118</v>
+        <v>-0.04561016012796217</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.1605429565028987</v>
+        <v>-0.1517045582676799</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.1440300765615676</v>
+        <v>-0.04806758509920873</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04999556853619143</v>
+        <v>-0.02744780216570267</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
         <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.05778347295057583</v>
+        <v>0.1108889174696215</v>
       </c>
       <c r="DY14" t="n">
         <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.0674115552838277</v>
+        <v>0.111147887372112</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.08252695482841645</v>
+        <v>0.02021855353888946</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
@@ -8226,28 +8226,28 @@
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.1289520860103432</v>
+        <v>-0.265037560835947</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.007454371641427857</v>
+        <v>0.1210059299870043</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.05983349005528493</v>
+        <v>0.1239891552313353</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
         <v>0</v>
@@ -8262,16 +8262,16 @@
         <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.02389308443521831</v>
+        <v>-0.1835669949229105</v>
       </c>
       <c r="EQ14" t="n">
         <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.1265947083357736</v>
+        <v>0.157791382451138</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.03083252200740298</v>
+        <v>0.02564120613229333</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8283,138 +8283,138 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.1730605982035738</v>
+        <v>-0.3393566946842945</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.1392480000548824</v>
+        <v>0.2173550889863674</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01952066603549044</v>
+        <v>0.0414311971106079</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.1080305165243792</v>
+        <v>-0.1634888897258523</v>
       </c>
       <c r="FI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>-0.03066121987233123</v>
+        <v>0.1423451268445427</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.03780009877150433</v>
+        <v>0.01774303409017373</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.0107076798189044</v>
+        <v>0.0415610148928758</v>
       </c>
       <c r="FR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.007078335424732777</v>
+        <v>0.1959614321007952</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.01900582118128482</v>
+        <v>-0.02199864321795938</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
         <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY14" t="n">
         <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.01155993864220486</v>
+        <v>-0.2647011620853089</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.04041453679957378</v>
+        <v>0.09818780599705623</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7739952147191567</v>
+        <v>-0.5149635499231863</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4687533989731902</v>
+        <v>0.09060333531960509</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1891857816705318</v>
+        <v>0.1200239204385978</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8423,22 +8423,22 @@
         <v>-0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.640772127829684</v>
+        <v>-0.4399665230020304</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3524027723952133</v>
+        <v>0.1992631834036707</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1752461491890104</v>
+        <v>0.1663101304715037</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -8447,82 +8447,82 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1642497480570302</v>
+        <v>-0.07657078119586477</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.005640032197203</v>
+        <v>0.06559082436531859</v>
       </c>
       <c r="W15" t="n">
-        <v>0.06376561778908978</v>
+        <v>-0.02885365665060645</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1639667660290684</v>
+        <v>-0.03786643884658146</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.02224843768651554</v>
+        <v>0.1302017576781793</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02257493978771179</v>
+        <v>-0.006759207367177084</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.05935337991450319</v>
+        <v>-0.2311596318251218</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.07284454745930288</v>
+        <v>0.05696816759291947</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.0653830724718384</v>
+        <v>-0.2212243571127898</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -8534,22 +8534,22 @@
         <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.3894779945521345</v>
+        <v>-0.4163314059334229</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.1075867400878485</v>
+        <v>0.08231857125758316</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.148477387349493</v>
+        <v>-0.04729342047541685</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>-0</v>
@@ -8558,19 +8558,19 @@
         <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.1626556297470318</v>
+        <v>0.04986132608450974</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0.1515930913522684</v>
+        <v>0.03871597080513677</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.2635582081474307</v>
+        <v>0.2270951266720848</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8585,73 +8585,73 @@
         <v>-0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.1256467119429057</v>
+        <v>0.1011947109599847</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0526372044823889</v>
+        <v>0.04248609143454574</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.1488459099524097</v>
+        <v>0.02674719768089989</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1833657307351888</v>
+        <v>-0.3740715424092684</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.06265335007485752</v>
+        <v>0.07087846643922496</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.08611449052643086</v>
+        <v>-0.03562287157513748</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.1142059879698003</v>
+        <v>0.2497344581940408</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.05593419158418832</v>
+        <v>-0.02658563547374574</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.009025246550427687</v>
+        <v>0.002049720264736161</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,46 +8669,46 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0714342391259539</v>
+        <v>0.2785356898663834</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.1431337384764385</v>
+        <v>-0.07335979265021739</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1966119624089456</v>
+        <v>-0.1582139035111772</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.1203719312725842</v>
+        <v>0.2458628630473395</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.08276299459095234</v>
+        <v>-0.03817613545418026</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.01521674420412942</v>
+        <v>-0.00566128303238242</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8723,16 +8723,16 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.07690948638249064</v>
+        <v>0.04402505912530909</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.1203080589860175</v>
+        <v>0.009455532191907539</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.02601791285663516</v>
+        <v>-0.003693602003610264</v>
       </c>
       <c r="DJ15" t="n">
         <v>0</v>
@@ -8741,52 +8741,52 @@
         <v>0</v>
       </c>
       <c r="DL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.004643044274379681</v>
+        <v>0.1331474595643804</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1641398478012508</v>
+        <v>0.01454921103690001</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.02751478908019808</v>
+        <v>0.001512618107041361</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06689639033277768</v>
+        <v>-0.01707986300790637</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0.07263940421580696</v>
+        <v>0.0106186696799408</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.01059719089154332</v>
+        <v>-0.1138336216978252</v>
       </c>
       <c r="EB15" t="n">
         <v>0</v>
@@ -8798,49 +8798,49 @@
         <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.1449170206266219</v>
+        <v>0.2287941676422428</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.1562746768301965</v>
+        <v>-0.0204086925957741</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03024090340202755</v>
+        <v>0.0009987320749868867</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.1550012043101075</v>
+        <v>0.1668756638022802</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.04770558027040574</v>
+        <v>-0.01084208472996667</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.09111015916245507</v>
+        <v>-0.09764413904650632</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
@@ -8849,7 +8849,7 @@
         <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>-0</v>
@@ -8858,25 +8858,25 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1155115213402834</v>
+        <v>0.2887296534081815</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.07141850579880391</v>
+        <v>-0.02226288622160845</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.004103350583980048</v>
+        <v>0.002615004809096181</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
         <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,25 +8885,25 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.02888397130636034</v>
+        <v>0.1652300212581544</v>
       </c>
       <c r="FI15" t="n">
         <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.1235308957146278</v>
+        <v>-0.08117358460442461</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.1078321830504056</v>
+        <v>0.02014794510476282</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,40 +8912,40 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.04128364859769069</v>
+        <v>0.02507952393725073</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.01130357296801947</v>
+        <v>-0.000143608715891538</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.01255504146166384</v>
+        <v>-0.01084659600872612</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
         <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07694043120274646</v>
+        <v>0.1360656942561953</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>-0.08759083563228098</v>
+        <v>0.08202956483803868</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
@@ -8954,12 +8954,1719 @@
         <v>-0</v>
       </c>
       <c r="GE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
       </c>
       <c r="GG15" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.2920974386208073</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.1537107940647464</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.06436824913015186</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.1701526086703879</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1101105023432042</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.03746552647196779</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.07480260195374351</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.1579440208048382</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.06630226781786783</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.008118830131167083</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.1952540446953915</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.1547409473588657</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.08916980233392938</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.1149454177966238</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.06167778621222255</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.1867798369269406</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.2954810450035511</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.1155717887749743</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.007050729843892237</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.3341175806392999</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.1245983776512492</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0.09495175184390255</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0.01993832531633147</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.1711190072005028</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0.1921734473883518</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0.4721640941074394</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0.01589007403913517</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.1161934694041345</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0.03650945935213955</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.005871304872802589</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.04363821418722977</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0.003113700016225753</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.09980917211490792</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0.09294691942542754</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-0.03637794652294243</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.02720045597055595</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0.03983293230874226</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>-0.08682687090652536</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.01524089351563583</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0.006709044461044414</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>-0.04746812833725485</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.09336440122335136</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0.01857857876631081</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>-0.005096599607415197</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0.1671696853484622</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0.06425792499222922</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0.08853635560219938</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>-0.05431599981214429</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0.02984299221056263</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>-0.09219111183062094</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0.03087306504333693</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0.1034824327058189</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>-0.07202477685613461</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.02034323179220354</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0.1996803095129471</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0.09964904500637542</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0.1957204433336254</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0.006192188214548633</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0.009744185887063628</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0.1236832521899815</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0.0881535080902848</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>-0.08687541828063423</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.3763158604554189</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1080141391846401</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5546883204510283</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.4244848803014127</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3020563847722151</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5531257601359224</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.1328820297918179</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1591727585895424</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.07463508423253692</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.02074293331063401</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.2724192447714864</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.177958715038015</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.1362826376378882</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.06278974348702805</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.138474158284885</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.5369607644488481</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.1275537172683595</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.3179149934108095</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.08773267130409113</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.2005009272158735</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.112746307415037</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.06960742287914121</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.157340729295455</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0.0004956035986791356</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.3855700875748046</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.1059758938056528</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>0.2326526023957651</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.1360277628193169</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.02551918049643501</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.1374393139109585</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.271803917662829</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.196700145587344</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-0.1352908610718352</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.09585904909154037</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.03301353707836732</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0.1513279787716155</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.1208610566917738</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.1620319132659268</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>-0.05051658856286744</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-0.02728467591851239</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.1046705593657865</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0.06108212727488813</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0.1488465353548438</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>0.001267429969933861</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>-0.08834468816434597</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.02674802746417302</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.01283877194094561</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>-0.03958636952913908</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.05110658939113159</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>0.03986652710772733</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0.2142259745708726</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.1589526390353068</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.005515511987697142</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>-0.1453811747045665</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0.1274923375991713</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0.1059137452034941</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>-0.1344136745025702</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>-0.001105904806268982</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>0.03734783214664512</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>-0.07367743185673462</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.04757569233216155</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>-0.00373573344233456</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG18" t="n">
         <v>-0</v>
       </c>
     </row>
